--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>83.72089437268842</v>
+        <v>13.60464533556187</v>
       </c>
       <c r="D2" t="n">
-        <v>83.62127379513103</v>
+        <v>13.58845699170879</v>
       </c>
       <c r="E2" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F2" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.49642760899707</v>
+        <v>3.493169486462024</v>
       </c>
       <c r="D3" t="n">
-        <v>21.21653028913284</v>
+        <v>3.447686171984087</v>
       </c>
       <c r="E3" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F3" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.582138452781805</v>
+        <v>1.557097498577043</v>
       </c>
       <c r="D4" t="n">
-        <v>9.247248484255135</v>
+        <v>1.502677878691459</v>
       </c>
       <c r="E4" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F4" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.85193081876386</v>
+        <v>3.063438758049128</v>
       </c>
       <c r="D5" t="n">
-        <v>18.61278826748602</v>
+        <v>3.024578093466479</v>
       </c>
       <c r="E5" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F5" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.00370753473505</v>
+        <v>2.113102474394446</v>
       </c>
       <c r="D6" t="n">
-        <v>13.27084637550504</v>
+        <v>2.156512536019569</v>
       </c>
       <c r="E6" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F6" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.91102873189359</v>
+        <v>8.435542168932708</v>
       </c>
       <c r="D7" t="n">
-        <v>52.19223005640057</v>
+        <v>8.481237384165093</v>
       </c>
       <c r="E7" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F7" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.41515541181078</v>
+        <v>2.992462754419251</v>
       </c>
       <c r="D8" t="n">
-        <v>18.715357970854</v>
+        <v>3.041245670263775</v>
       </c>
       <c r="E8" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F8" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.43491024461902</v>
+        <v>3.808172914750591</v>
       </c>
       <c r="D9" t="n">
-        <v>23.76982589951714</v>
+        <v>3.862596708671536</v>
       </c>
       <c r="E9" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F9" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.48088051746902</v>
+        <v>7.878143084088717</v>
       </c>
       <c r="D10" t="n">
-        <v>48.38552252440829</v>
+        <v>7.862647410216348</v>
       </c>
       <c r="E10" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F10" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.13459180785725</v>
+        <v>5.221871168776803</v>
       </c>
       <c r="D11" t="n">
-        <v>32.1815124956582</v>
+        <v>5.229495780544458</v>
       </c>
       <c r="E11" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F11" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.55097564859693</v>
+        <v>4.964533542897001</v>
       </c>
       <c r="D12" t="n">
-        <v>30.75644314489859</v>
+        <v>4.99792201104602</v>
       </c>
       <c r="E12" t="n">
-        <v>20.77968089409951</v>
+        <v>3.37669814529117</v>
       </c>
       <c r="F12" t="n">
-        <v>20.78184028328507</v>
+        <v>3.377049046033825</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
